--- a/data/trans_orig/CoPsoQ-Clase-trans_orig.xlsx
+++ b/data/trans_orig/CoPsoQ-Clase-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2012</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,97 +732,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2048</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,12%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2078</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>169741</t>
+          <t>171023</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>205144</t>
+          <t>206058</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>57,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94256</t>
+          <t>92599</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>123123</t>
+          <t>122341</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>274463</t>
+          <t>273813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>319565</t>
+          <t>319375</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44660</t>
+          <t>42573</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72315</t>
+          <t>72302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29776</t>
+          <t>30134</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54148</t>
+          <t>54821</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>81423</t>
+          <t>80364</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>117103</t>
+          <t>119936</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>24,57%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42525</t>
+          <t>41627</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71915</t>
+          <t>69714</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>27956</t>
+          <t>28359</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52134</t>
+          <t>51186</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77209</t>
+          <t>77124</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>113231</t>
+          <t>111906</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>22,93%</t>
         </is>
       </c>
     </row>
@@ -1301,97 +1301,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2119</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156517</t>
+          <t>156544</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>189375</t>
+          <t>188993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>61,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>74,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>68758</t>
+          <t>69267</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94695</t>
+          <t>96145</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>230357</t>
+          <t>233116</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>274221</t>
+          <t>276562</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,06%</t>
+          <t>55,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>65,55%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30574</t>
+          <t>30174</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55081</t>
+          <t>55266</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>37096</t>
+          <t>36561</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62124</t>
+          <t>61140</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72942</t>
+          <t>72470</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109038</t>
+          <t>109626</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,2%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>27612</t>
+          <t>26291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>52668</t>
+          <t>53312</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24355</t>
+          <t>24648</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45113</t>
+          <t>45998</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>58134</t>
+          <t>57621</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>92221</t>
+          <t>91813</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,95%</t>
         </is>
       </c>
     </row>
@@ -1870,97 +1870,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,72%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,86%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1978</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>134385</t>
+          <t>133983</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>166622</t>
+          <t>169431</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>48,94%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,86%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52050</t>
+          <t>50846</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>72210</t>
+          <t>71364</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>47,31%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>194752</t>
+          <t>195186</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>232556</t>
+          <t>231068</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,61%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35602</t>
+          <t>35005</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60283</t>
+          <t>60119</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>21,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14893</t>
+          <t>14477</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>31863</t>
+          <t>32367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54505</t>
+          <t>54644</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84620</t>
+          <t>84600</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61510</t>
+          <t>61796</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>90653</t>
+          <t>91135</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16073</t>
+          <t>16172</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32172</t>
+          <t>33331</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>82770</t>
+          <t>84060</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117375</t>
+          <t>117192</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -2439,97 +2439,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2037</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>196543</t>
+          <t>197515</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>240232</t>
+          <t>241216</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,25%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153768</t>
+          <t>153928</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188081</t>
+          <t>188568</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>361442</t>
+          <t>361988</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>416412</t>
+          <t>416725</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>75956</t>
+          <t>74827</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>112704</t>
+          <t>110002</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,1%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>38451</t>
+          <t>37562</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65065</t>
+          <t>65208</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120957</t>
+          <t>120804</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>164178</t>
+          <t>166194</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,1%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>86173</t>
+          <t>88117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125984</t>
+          <t>125981</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,7 +2793,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>60052</t>
+          <t>59380</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>89954</t>
+          <t>90473</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,52%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156403</t>
+          <t>156674</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>205900</t>
+          <t>204684</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,01%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,97%</t>
+          <t>28,8%</t>
         </is>
       </c>
     </row>
@@ -3008,97 +3008,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>1,35%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>2092</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67371</t>
+          <t>67098</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91628</t>
+          <t>91776</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,97%</t>
+          <t>44,78%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68185</t>
+          <t>68294</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94722</t>
+          <t>94177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>144317</t>
+          <t>143023</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>180551</t>
+          <t>180238</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,77%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22675</t>
+          <t>22511</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>41648</t>
+          <t>42947</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>28,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>32901</t>
+          <t>33398</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57653</t>
+          <t>56927</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>19,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>61221</t>
+          <t>62519</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>93011</t>
+          <t>92217</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28147</t>
+          <t>28487</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49051</t>
+          <t>49125</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>37376</t>
+          <t>36230</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>60998</t>
+          <t>60688</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>71335</t>
+          <t>71753</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>103885</t>
+          <t>104935</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3432,12 +3432,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,47%</t>
         </is>
       </c>
     </row>
@@ -4146,97 +4146,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>2079</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>2059</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>769749</t>
+          <t>774730</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>846847</t>
+          <t>848278</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>472183</t>
+          <t>469687</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>532756</t>
+          <t>534587</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>50,84%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,36%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1262592</t>
+          <t>1269457</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1362660</t>
+          <t>1370213</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>54,38%</t>
+          <t>54,68%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>58,69%</t>
+          <t>59,02%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>236265</t>
+          <t>240014</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>298568</t>
+          <t>300717</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>182765</t>
+          <t>181284</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>231805</t>
+          <t>232626</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>437644</t>
+          <t>432411</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>517798</t>
+          <t>513223</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,11%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>284968</t>
+          <t>280709</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>350336</t>
+          <t>345507</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,15%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>193059</t>
+          <t>195098</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>246162</t>
+          <t>245692</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,5%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>491825</t>
+          <t>490640</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>572755</t>
+          <t>576318</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,82%</t>
         </is>
       </c>
     </row>
@@ -4754,7 +4754,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2016</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4949,97 +4949,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1957</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138532</t>
+          <t>139449</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172580</t>
+          <t>172111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>50,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,0%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107437</t>
+          <t>107046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136506</t>
+          <t>136747</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,16%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>63,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>257146</t>
+          <t>254579</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>301173</t>
+          <t>300116</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>52,21%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51100</t>
+          <t>50820</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>79742</t>
+          <t>80752</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,65%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36250</t>
+          <t>36419</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60666</t>
+          <t>61045</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,5%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94457</t>
+          <t>95851</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133673</t>
+          <t>133039</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,14%</t>
+          <t>27,01%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44352</t>
+          <t>44031</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>72126</t>
+          <t>71323</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32299</t>
+          <t>33544</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56843</t>
+          <t>56952</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83781</t>
+          <t>83917</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>118248</t>
+          <t>119820</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,33%</t>
         </is>
       </c>
     </row>
@@ -5518,97 +5518,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2081</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1983</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>124961</t>
+          <t>125668</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>157469</t>
+          <t>158927</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,5%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>64,53%</t>
+          <t>65,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>91432</t>
+          <t>92470</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119516</t>
+          <t>119290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>63,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>224523</t>
+          <t>225101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266380</t>
+          <t>266939</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>51,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>61,62%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42421</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69626</t>
+          <t>69636</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>27304</t>
+          <t>28037</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50819</t>
+          <t>49440</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>74150</t>
+          <t>76851</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>111567</t>
+          <t>113083</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,1%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36704</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62019</t>
+          <t>64087</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>32929</t>
+          <t>34172</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>57210</t>
+          <t>56919</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77392</t>
+          <t>77478</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>111850</t>
+          <t>112335</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,82%</t>
+          <t>25,93%</t>
         </is>
       </c>
     </row>
@@ -6087,97 +6087,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2033</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2015</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>115046</t>
+          <t>113958</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>144310</t>
+          <t>143725</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,95%</t>
+          <t>52,45%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,42%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24579</t>
+          <t>24629</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40268</t>
+          <t>40840</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>60,77%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145031</t>
+          <t>145621</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>178622</t>
+          <t>179703</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>50,98%</t>
+          <t>51,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>62,79%</t>
+          <t>63,17%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>38194</t>
+          <t>36135</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>63230</t>
+          <t>62924</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>11007</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26234</t>
+          <t>25535</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52651</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>82718</t>
+          <t>83002</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,18%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28114</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51833</t>
+          <t>52411</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10501</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24062</t>
+          <t>24958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,81%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42765</t>
+          <t>41600</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70933</t>
+          <t>69294</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -6656,97 +6656,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,41%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1941</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,53%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1987</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244355</t>
+          <t>244048</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>289275</t>
+          <t>287081</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>207548</t>
+          <t>206702</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>246211</t>
+          <t>244554</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>56,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>66,45%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>466074</t>
+          <t>461882</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>525413</t>
+          <t>523088</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,4%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,05%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>85913</t>
+          <t>86373</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123638</t>
+          <t>123160</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62198</t>
+          <t>62806</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>92829</t>
+          <t>93447</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>154047</t>
+          <t>157077</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>204816</t>
+          <t>204309</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>23,85%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99977</t>
+          <t>99548</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>139644</t>
+          <t>137591</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50129</t>
+          <t>50293</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>79430</t>
+          <t>80011</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>158433</t>
+          <t>158912</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206929</t>
+          <t>207099</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,17%</t>
         </is>
       </c>
     </row>
@@ -7225,97 +7225,97 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>2091</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="R24" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72619</t>
+          <t>72878</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>101178</t>
+          <t>102050</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,61%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71189</t>
+          <t>69617</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>97574</t>
+          <t>98188</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>151297</t>
+          <t>150795</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>193077</t>
+          <t>189809</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,31%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>37960</t>
+          <t>38315</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>62357</t>
+          <t>63280</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,15%</t>
+          <t>32,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>33645</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57269</t>
+          <t>57092</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>78068</t>
+          <t>77126</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112280</t>
+          <t>111343</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,43%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44081</t>
+          <t>44823</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>70256</t>
+          <t>71558</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>56255</t>
+          <t>55466</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>82576</t>
+          <t>81885</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>110387</t>
+          <t>108999</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>147180</t>
+          <t>147020</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -8363,97 +8363,97 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>2063</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="R34" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>1964</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P34" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S34" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T34" s="2" t="inlineStr">
-        <is>
-          <t>2021</t>
-        </is>
-      </c>
-      <c r="U34" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>740569</t>
+          <t>745027</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>818182</t>
+          <t>821252</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>52,07%</t>
+          <t>52,38%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>539800</t>
+          <t>540032</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>604079</t>
+          <t>603968</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>52,12%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,29%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1300784</t>
+          <t>1301352</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1403970</t>
+          <t>1402191</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>57,03%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>290444</t>
+          <t>289544</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>353247</t>
+          <t>353561</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>198662</t>
+          <t>200265</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>252228</t>
+          <t>253631</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,17%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>505071</t>
+          <t>501500</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>589857</t>
+          <t>588530</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>23,94%</t>
         </is>
       </c>
     </row>
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>289092</t>
+          <t>288229</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>356541</t>
+          <t>353114</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>214627</t>
+          <t>213122</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>268564</t>
+          <t>270379</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,57%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,09%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>514449</t>
+          <t>520071</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>600326</t>
+          <t>606554</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>20,92%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,67%</t>
         </is>
       </c>
     </row>
@@ -8971,7 +8971,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>CoPsoQ - Exigencias psicológicas en 2023</t>
+          <t>CoPsoQ - Exigencias psicológicas en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9166,12 +9166,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>360662</t>
+          <t>361745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>397101</t>
+          <t>398035</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9181,12 +9181,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321488</t>
+          <t>321615</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>348899</t>
+          <t>349805</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9236,12 +9236,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>690824</t>
+          <t>690879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>737139</t>
+          <t>737296</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>83,32%</t>
         </is>
       </c>
     </row>
@@ -9279,12 +9279,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24817</t>
+          <t>23922</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>49794</t>
+          <t>50724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9314,12 +9314,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20809</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38877</t>
+          <t>38127</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9349,12 +9349,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>50759</t>
+          <t>49846</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>81049</t>
+          <t>82653</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12930</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31870</t>
+          <t>30967</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11336</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>24883</t>
+          <t>26067</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>29351</t>
+          <t>28254</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52490</t>
+          <t>52341</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22431</t>
+          <t>21329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47396</t>
+          <t>47486</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24397</t>
+          <t>24703</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>45715</t>
+          <t>44674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51647</t>
+          <t>51989</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84741</t>
+          <t>84128</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -9735,12 +9735,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>329330</t>
+          <t>329324</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>360865</t>
+          <t>361691</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,1%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9770,12 +9770,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>269530</t>
+          <t>269604</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>295369</t>
+          <t>295343</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,07%</t>
+          <t>78,09%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>608938</t>
+          <t>606068</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>649545</t>
+          <t>648197</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>80,17%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>85,34%</t>
         </is>
       </c>
     </row>
@@ -9848,12 +9848,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>16206</t>
+          <t>15950</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>37867</t>
+          <t>38854</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9863,12 +9863,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17214</t>
+          <t>17104</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35105</t>
+          <t>34863</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36999</t>
+          <t>37693</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>67295</t>
+          <t>65594</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>11318</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>28077</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8610</t>
+          <t>8578</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21714</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>22330</t>
+          <t>23181</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>44972</t>
+          <t>45817</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>15321</t>
+          <t>14886</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34233</t>
+          <t>34048</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15565</t>
+          <t>16515</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>34181</t>
+          <t>33967</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>35561</t>
+          <t>36522</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61504</t>
+          <t>62578</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -10304,12 +10304,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135810</t>
+          <t>111550</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>533492</t>
+          <t>529314</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10319,12 +10319,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107776</t>
+          <t>107863</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>125714</t>
+          <t>124694</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,21%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>190730</t>
+          <t>189489</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>647552</t>
+          <t>649166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,72%</t>
+          <t>83,92%</t>
         </is>
       </c>
     </row>
@@ -10417,12 +10417,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8340</t>
+          <t>8185</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53148</t>
+          <t>51737</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10432,12 +10432,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9336</t>
+          <t>8903</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25445</t>
+          <t>23849</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10467,12 +10467,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>15103</t>
+          <t>13532</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>70750</t>
+          <t>72428</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10502,12 +10502,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -10530,12 +10530,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4553</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34070</t>
+          <t>34417</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10545,12 +10545,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9729</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10580,12 +10580,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>7754</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39722</t>
+          <t>39198</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10615,12 +10615,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -10643,12 +10643,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>27984</t>
+          <t>28304</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>479670</t>
+          <t>502517</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10658,12 +10658,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,11%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10678,12 +10678,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2626</t>
+          <t>2512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11138</t>
+          <t>10739</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10693,12 +10693,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10713,12 +10713,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>32516</t>
+          <t>31165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>556235</t>
+          <t>552356</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10728,12 +10728,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,41%</t>
         </is>
       </c>
     </row>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>778052</t>
+          <t>777342</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>823222</t>
+          <t>822761</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10888,12 +10888,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>83,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>746077</t>
+          <t>745207</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>835025</t>
+          <t>841533</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,11%</t>
+          <t>84,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1541176</t>
+          <t>1546420</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1656399</t>
+          <t>1657002</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10958,12 +10958,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,34%</t>
         </is>
       </c>
     </row>
@@ -10986,12 +10986,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35424</t>
+          <t>35027</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>64604</t>
+          <t>65397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27071</t>
+          <t>23917</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78551</t>
+          <t>78007</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>72339</t>
+          <t>68708</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>129523</t>
+          <t>126715</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11071,12 +11071,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -11099,12 +11099,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>25394</t>
+          <t>27859</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>52968</t>
+          <t>54540</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12259</t>
+          <t>11431</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>38910</t>
+          <t>39236</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11169,12 +11169,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43599</t>
+          <t>43153</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>85315</t>
+          <t>84120</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11184,12 +11184,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,64%</t>
         </is>
       </c>
     </row>
@@ -11212,12 +11212,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26212</t>
+          <t>26703</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54018</t>
+          <t>54207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8870</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32463</t>
+          <t>32470</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11262,7 +11262,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>39681</t>
+          <t>38536</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>78907</t>
+          <t>76601</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11297,12 +11297,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>317871</t>
+          <t>319602</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>357648</t>
+          <t>355339</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11457,12 +11457,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,52%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,19%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11477,12 +11477,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>626148</t>
+          <t>626296</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>666566</t>
+          <t>666998</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11492,12 +11492,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,13%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11512,12 +11512,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>953991</t>
+          <t>955647</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1015374</t>
+          <t>1017719</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11527,12 +11527,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,36%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,99%</t>
         </is>
       </c>
     </row>
@@ -11555,12 +11555,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18395</t>
+          <t>18830</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>41428</t>
+          <t>42628</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -11570,12 +11570,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11590,12 +11590,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>24387</t>
+          <t>23732</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>49189</t>
+          <t>48423</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -11605,12 +11605,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11625,12 +11625,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48761</t>
+          <t>48383</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>83892</t>
+          <t>81214</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -11640,12 +11640,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -11668,12 +11668,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14130</t>
+          <t>14473</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36278</t>
+          <t>37200</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -11683,12 +11683,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -11703,12 +11703,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>11563</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>27560</t>
+          <t>26971</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -11718,12 +11718,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11738,12 +11738,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>30501</t>
+          <t>29344</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>58423</t>
+          <t>60187</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -11753,12 +11753,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -11781,12 +11781,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11458</t>
+          <t>11907</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>44017</t>
+          <t>39973</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11500</t>
+          <t>11983</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28023</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11851,12 +11851,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>27270</t>
+          <t>26390</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>61000</t>
+          <t>59547</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,27%</t>
         </is>
       </c>
     </row>
@@ -12011,12 +12011,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>178014</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>182119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -12026,12 +12026,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -12046,12 +12046,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>578221</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>579488</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -12061,12 +12061,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,78%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -12081,12 +12081,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>760086</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>761606</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -12096,12 +12096,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>99,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12124,97 +12124,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>4105</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>1520</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12237,97 +12237,97 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>4105</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="R31" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U31" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S31" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T31" s="2" t="inlineStr">
-        <is>
-          <t>1520</t>
-        </is>
-      </c>
-      <c r="U31" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12350,97 +12350,97 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>4105</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="R32" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O32" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P32" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>1520</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>0,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -12580,12 +12580,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1794056</t>
+          <t>1766967</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2595396</t>
+          <t>2596374</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -12595,12 +12595,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>59,11%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2703335</t>
+          <t>2701954</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2817406</t>
+          <t>2816351</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -12630,12 +12630,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>87,46%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,17%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12650,12 +12650,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4287132</t>
+          <t>4363683</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5356240</t>
+          <t>5363764</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -12665,12 +12665,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,58%</t>
         </is>
       </c>
     </row>
@@ -12693,12 +12693,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>123095</t>
+          <t>124220</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>200207</t>
+          <t>200226</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -12708,7 +12708,7 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
@@ -12728,12 +12728,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>125401</t>
+          <t>124985</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>186521</t>
+          <t>187129</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -12743,12 +12743,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -12763,12 +12763,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>274764</t>
+          <t>276438</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>368443</t>
+          <t>368534</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
@@ -12806,12 +12806,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>84868</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>144876</t>
+          <t>147508</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -12821,12 +12821,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12841,12 +12841,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>62076</t>
+          <t>61558</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>97914</t>
+          <t>99312</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -12856,12 +12856,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12876,12 +12876,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>165011</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>235817</t>
+          <t>236305</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -12891,12 +12891,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,86%</t>
         </is>
       </c>
     </row>
@@ -12919,12 +12919,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>137469</t>
+          <t>136135</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1031530</t>
+          <t>1052965</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -12934,12 +12934,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>34,69%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12954,12 +12954,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>80619</t>
+          <t>81108</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>123346</t>
+          <t>125689</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -12969,12 +12969,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12989,12 +12989,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>235175</t>
+          <t>231711</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1386128</t>
+          <t>1306720</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -13004,12 +13004,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>21,34%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/CoPsoQ-Clase-trans_orig.xlsx
+++ b/data/trans_orig/CoPsoQ-Clase-trans_orig.xlsx
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>171023</t>
+          <t>169993</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>206058</t>
+          <t>206311</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,72%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92599</t>
+          <t>94334</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>122341</t>
+          <t>121063</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>50,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>273813</t>
+          <t>273303</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>319375</t>
+          <t>319576</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,1%</t>
+          <t>56,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>65,43%</t>
+          <t>65,48%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42573</t>
+          <t>43714</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>72302</t>
+          <t>70308</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>30134</t>
+          <t>31888</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>54821</t>
+          <t>54876</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>80364</t>
+          <t>80982</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>119936</t>
+          <t>118135</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,2%</t>
         </is>
       </c>
     </row>
@@ -1071,12 +1071,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>41627</t>
+          <t>41591</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69714</t>
+          <t>70471</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1086,12 +1086,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>23,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>28359</t>
+          <t>28520</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51186</t>
+          <t>50232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>26,69%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77124</t>
+          <t>76521</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>111906</t>
+          <t>112145</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>22,98%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>156544</t>
+          <t>155093</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>188993</t>
+          <t>188439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>74,58%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>69267</t>
+          <t>68002</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96145</t>
+          <t>95886</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>41,99%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233116</t>
+          <t>232446</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>276562</t>
+          <t>276172</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>55,72%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>66,01%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>30174</t>
+          <t>30009</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>55266</t>
+          <t>55420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36561</t>
+          <t>37796</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61140</t>
+          <t>61925</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>72470</t>
+          <t>73707</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>109626</t>
+          <t>108270</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>25,88%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26291</t>
+          <t>27635</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>53312</t>
+          <t>54010</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24648</t>
+          <t>24166</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>45998</t>
+          <t>46136</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>57621</t>
+          <t>57300</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>91813</t>
+          <t>91620</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -1983,12 +1983,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>133983</t>
+          <t>134994</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>169431</t>
+          <t>167746</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50846</t>
+          <t>51209</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>71364</t>
+          <t>72057</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2033,12 +2033,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>47,31%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2053,12 +2053,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>195186</t>
+          <t>194511</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>231068</t>
+          <t>232902</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2068,12 +2068,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>35005</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>60119</t>
+          <t>58858</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14477</t>
+          <t>14395</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32367</t>
+          <t>31561</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54644</t>
+          <t>54687</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>84600</t>
+          <t>85409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,4%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>61796</t>
+          <t>60172</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>91135</t>
+          <t>90740</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16172</t>
+          <t>15466</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33331</t>
+          <t>32375</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84060</t>
+          <t>83616</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>117192</t>
+          <t>119780</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>31,42%</t>
         </is>
       </c>
     </row>
@@ -2552,12 +2552,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>197515</t>
+          <t>196891</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>241216</t>
+          <t>238640</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2567,12 +2567,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2587,12 +2587,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153928</t>
+          <t>152678</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>188568</t>
+          <t>187151</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>361988</t>
+          <t>362552</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>416725</t>
+          <t>416339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,58%</t>
         </is>
       </c>
     </row>
@@ -2665,12 +2665,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>74827</t>
+          <t>74939</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>110002</t>
+          <t>109340</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2680,12 +2680,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2700,12 +2700,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37562</t>
+          <t>37293</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65208</t>
+          <t>64298</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2735,12 +2735,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>120804</t>
+          <t>121761</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>166194</t>
+          <t>164699</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,17%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>88117</t>
+          <t>88189</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>125981</t>
+          <t>124853</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>21,18%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59380</t>
+          <t>59754</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>90473</t>
+          <t>89567</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>156674</t>
+          <t>157275</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>204684</t>
+          <t>205848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,8%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -3121,12 +3121,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>67098</t>
+          <t>67140</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>91776</t>
+          <t>92353</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3136,12 +3136,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>44,78%</t>
+          <t>44,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>68294</t>
+          <t>67551</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>94177</t>
+          <t>95398</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>55,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3191,12 +3191,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>143023</t>
+          <t>141249</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>180238</t>
+          <t>178539</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>43,7%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,24%</t>
         </is>
       </c>
     </row>
@@ -3234,12 +3234,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22511</t>
+          <t>22537</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>42947</t>
+          <t>42886</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3249,12 +3249,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3269,12 +3269,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33398</t>
+          <t>33209</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>56927</t>
+          <t>56814</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3284,12 +3284,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3304,12 +3304,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>62519</t>
+          <t>62068</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>92217</t>
+          <t>92405</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,59%</t>
         </is>
       </c>
     </row>
@@ -3347,12 +3347,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>28487</t>
+          <t>28611</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>49125</t>
+          <t>50192</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3382,12 +3382,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>37241</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>60688</t>
+          <t>61765</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3397,12 +3397,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3417,12 +3417,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>71753</t>
+          <t>71761</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>104935</t>
+          <t>103612</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,06%</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>774730</t>
+          <t>767735</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>848278</t>
+          <t>844525</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4274,12 +4274,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>55,62%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>60,63%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>469687</t>
+          <t>470536</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>534587</t>
+          <t>534354</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1269457</t>
+          <t>1265943</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1370213</t>
+          <t>1364162</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>59,02%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -4372,12 +4372,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>240014</t>
+          <t>238459</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>300717</t>
+          <t>300433</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4407,12 +4407,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>181284</t>
+          <t>183497</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>232626</t>
+          <t>235905</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4422,12 +4422,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4442,12 +4442,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>432411</t>
+          <t>434119</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>513223</t>
+          <t>513624</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4457,12 +4457,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,7%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4485,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>280709</t>
+          <t>284308</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>345507</t>
+          <t>350478</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4500,12 +4500,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,41%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4520,12 +4520,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>195098</t>
+          <t>191829</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>245692</t>
+          <t>245807</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4535,12 +4535,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,45%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4555,12 +4555,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>490640</t>
+          <t>490964</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>576318</t>
+          <t>571919</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4570,12 +4570,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,13%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,63%</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5062,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>139449</t>
+          <t>139928</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>172111</t>
+          <t>173729</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5077,12 +5077,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>107046</t>
+          <t>107952</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>136747</t>
+          <t>136568</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5112,12 +5112,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,98%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5132,12 +5132,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>254579</t>
+          <t>257193</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>300116</t>
+          <t>303161</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5147,12 +5147,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,55%</t>
         </is>
       </c>
     </row>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50820</t>
+          <t>50987</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>80752</t>
+          <t>81190</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5210,12 +5210,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>36419</t>
+          <t>36800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61045</t>
+          <t>60330</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5225,12 +5225,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5245,12 +5245,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>95851</t>
+          <t>95182</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>133039</t>
+          <t>134830</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5260,12 +5260,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,46%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,01%</t>
+          <t>27,38%</t>
         </is>
       </c>
     </row>
@@ -5288,12 +5288,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>44031</t>
+          <t>43968</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>71323</t>
+          <t>71243</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5303,12 +5303,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,62%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5323,12 +5323,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>33544</t>
+          <t>32413</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56952</t>
+          <t>57054</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5358,12 +5358,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83917</t>
+          <t>82422</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119820</t>
+          <t>120947</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5373,12 +5373,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,56%</t>
         </is>
       </c>
     </row>
@@ -5631,12 +5631,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>125668</t>
+          <t>124440</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>158927</t>
+          <t>156968</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5646,12 +5646,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>65,13%</t>
+          <t>64,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5666,12 +5666,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>92470</t>
+          <t>92353</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>119290</t>
+          <t>119427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,82%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,06%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5701,12 +5701,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>225101</t>
+          <t>223729</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>266939</t>
+          <t>267038</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5716,12 +5716,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>51,96%</t>
+          <t>51,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>61,64%</t>
         </is>
       </c>
     </row>
@@ -5744,12 +5744,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>42001</t>
+          <t>42567</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>69636</t>
+          <t>69524</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5759,12 +5759,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5779,12 +5779,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28037</t>
+          <t>27732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49440</t>
+          <t>49963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5794,12 +5794,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5814,12 +5814,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76851</t>
+          <t>74851</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>113083</t>
+          <t>111740</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5829,12 +5829,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>25,79%</t>
         </is>
       </c>
     </row>
@@ -5857,12 +5857,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36194</t>
+          <t>36149</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>64087</t>
+          <t>63026</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5872,12 +5872,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5892,12 +5892,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>34172</t>
+          <t>34979</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56919</t>
+          <t>57282</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5907,12 +5907,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5927,12 +5927,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77478</t>
+          <t>77220</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>112335</t>
+          <t>114195</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5942,12 +5942,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,36%</t>
         </is>
       </c>
     </row>
@@ -6200,12 +6200,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>113958</t>
+          <t>113520</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>143725</t>
+          <t>144460</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>52,45%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>66,49%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>24629</t>
+          <t>25357</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>40840</t>
+          <t>41218</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6250,12 +6250,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6270,12 +6270,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>145621</t>
+          <t>145105</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>179703</t>
+          <t>177984</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6285,12 +6285,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,57%</t>
         </is>
       </c>
     </row>
@@ -6313,12 +6313,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36135</t>
+          <t>37458</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62924</t>
+          <t>63430</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6328,12 +6328,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6348,12 +6348,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11007</t>
+          <t>11020</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>25252</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6363,12 +6363,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52530</t>
+          <t>52852</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83002</t>
+          <t>82946</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6398,12 +6398,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>29,16%</t>
         </is>
       </c>
     </row>
@@ -6426,12 +6426,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>27762</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52411</t>
+          <t>50734</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6461,12 +6461,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11073</t>
+          <t>11042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24958</t>
+          <t>24252</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6496,12 +6496,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41600</t>
+          <t>44111</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69294</t>
+          <t>70316</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6511,12 +6511,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,72%</t>
         </is>
       </c>
     </row>
@@ -6769,12 +6769,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244048</t>
+          <t>243422</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>287081</t>
+          <t>288474</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6784,12 +6784,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6804,12 +6804,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>206702</t>
+          <t>208493</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>244554</t>
+          <t>245756</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>461882</t>
+          <t>466706</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>523088</t>
+          <t>522731</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,01%</t>
         </is>
       </c>
     </row>
@@ -6882,12 +6882,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>86373</t>
+          <t>85991</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>123160</t>
+          <t>123474</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6897,12 +6897,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6917,12 +6917,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62806</t>
+          <t>60651</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93447</t>
+          <t>91228</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,79%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>157077</t>
+          <t>157241</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>204309</t>
+          <t>205616</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -6995,12 +6995,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>99548</t>
+          <t>100331</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>137591</t>
+          <t>138803</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7010,12 +7010,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7030,12 +7030,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>50293</t>
+          <t>50609</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80011</t>
+          <t>79432</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>158912</t>
+          <t>160349</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207099</t>
+          <t>206024</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,05%</t>
         </is>
       </c>
     </row>
@@ -7338,12 +7338,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>72878</t>
+          <t>72592</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>102050</t>
+          <t>100028</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7353,12 +7353,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,57%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>52,61%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7373,12 +7373,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>69617</t>
+          <t>69739</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98188</t>
+          <t>99078</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>49,69%</t>
+          <t>50,14%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>150795</t>
+          <t>151171</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>189809</t>
+          <t>190764</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>38,51%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -7451,12 +7451,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>38315</t>
+          <t>37414</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>63280</t>
+          <t>62998</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7466,12 +7466,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>32,62%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7486,12 +7486,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33645</t>
+          <t>32300</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>57092</t>
+          <t>56080</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7501,12 +7501,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7521,12 +7521,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>77126</t>
+          <t>76214</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>111343</t>
+          <t>111046</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7536,12 +7536,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,36%</t>
         </is>
       </c>
     </row>
@@ -7564,12 +7564,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44823</t>
+          <t>45916</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71558</t>
+          <t>71359</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7579,12 +7579,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>36,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>55466</t>
+          <t>55823</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>81885</t>
+          <t>83874</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7614,12 +7614,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7634,12 +7634,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>108999</t>
+          <t>107280</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>147020</t>
+          <t>146097</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7649,12 +7649,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>37,31%</t>
         </is>
       </c>
     </row>
@@ -7774,7 +7774,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>745027</t>
+          <t>741230</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>821252</t>
+          <t>819477</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>52,38%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8511,12 +8511,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>540032</t>
+          <t>537185</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>603968</t>
+          <t>605370</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8526,12 +8526,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>52,12%</t>
+          <t>51,84%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>58,29%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8546,12 +8546,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1301352</t>
+          <t>1302257</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1402191</t>
+          <t>1399094</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8561,12 +8561,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -8589,12 +8589,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>289544</t>
+          <t>287833</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>353561</t>
+          <t>355907</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>24,86%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8624,12 +8624,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>200265</t>
+          <t>199810</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>253631</t>
+          <t>251948</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8639,12 +8639,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>19,28%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>501500</t>
+          <t>502247</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>588530</t>
+          <t>588602</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>288229</t>
+          <t>289109</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>353114</t>
+          <t>353064</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8717,12 +8717,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8737,12 +8737,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>213122</t>
+          <t>211422</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>270379</t>
+          <t>267585</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8752,12 +8752,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20,57%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8772,12 +8772,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>520071</t>
+          <t>521738</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>606554</t>
+          <t>602550</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8787,12 +8787,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,51%</t>
         </is>
       </c>
     </row>
@@ -9161,32 +9161,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>380383</t>
+          <t>411881</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>361745</t>
+          <t>390729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>398035</t>
+          <t>432176</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,8%</t>
+          <t>84,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9196,32 +9196,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>335432</t>
+          <t>367028</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>321615</t>
+          <t>350510</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>349805</t>
+          <t>381210</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9231,32 +9231,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>715815</t>
+          <t>778910</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>690879</t>
+          <t>751759</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>737296</t>
+          <t>802358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>80,89%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,23%</t>
         </is>
       </c>
     </row>
@@ -9274,17 +9274,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>35588</t>
+          <t>38785</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23922</t>
+          <t>26421</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>50724</t>
+          <t>55196</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9294,12 +9294,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9309,67 +9309,67 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>28595</t>
+          <t>30245</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>22206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38127</t>
+          <t>41027</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
+          <t>9,07%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>69030</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>54846</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>88531</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
           <t>9,18%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>64182</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>49846</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>82653</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>7,25%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
         </is>
       </c>
     </row>
@@ -9387,32 +9387,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>26929</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>18005</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>30967</t>
+          <t>42783</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9422,32 +9422,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17711</t>
+          <t>18330</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>11925</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>26067</t>
+          <t>26504</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9457,32 +9457,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>38607</t>
+          <t>45259</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>28254</t>
+          <t>32566</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52341</t>
+          <t>60741</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>32513</t>
+          <t>34292</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21329</t>
+          <t>23751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47486</t>
+          <t>50526</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>33769</t>
+          <t>36513</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>24703</t>
+          <t>26331</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>44674</t>
+          <t>48727</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>66283</t>
+          <t>70805</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>51989</t>
+          <t>55080</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>84128</t>
+          <t>90294</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -9613,17 +9613,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>469380</t>
+          <t>511888</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>469380</t>
+          <t>511888</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>469380</t>
+          <t>511888</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9648,17 +9648,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>415507</t>
+          <t>452116</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>415507</t>
+          <t>452116</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>415507</t>
+          <t>452116</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9683,17 +9683,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>884887</t>
+          <t>964004</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>884887</t>
+          <t>964004</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>884887</t>
+          <t>964004</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9730,32 +9730,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>346309</t>
+          <t>367660</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>329324</t>
+          <t>349344</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>361691</t>
+          <t>382936</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,4%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>79,49%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>86,86%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -9765,32 +9765,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>283219</t>
+          <t>313685</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>269604</t>
+          <t>297421</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>295343</t>
+          <t>325354</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>78,09%</t>
+          <t>78,07%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -9800,32 +9800,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>629527</t>
+          <t>681344</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>606068</t>
+          <t>655342</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>648197</t>
+          <t>699753</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>82,88%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>79,8%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,15%</t>
         </is>
       </c>
     </row>
@@ -9843,32 +9843,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>27644</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15950</t>
+          <t>17998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38854</t>
+          <t>42450</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9878,22 +9878,22 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>26949</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17104</t>
+          <t>18872</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34863</t>
+          <t>38621</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -9903,7 +9903,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9913,32 +9913,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>50375</t>
+          <t>54593</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>37693</t>
+          <t>41494</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65594</t>
+          <t>71980</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,76%</t>
         </is>
       </c>
     </row>
@@ -9956,32 +9956,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18581</t>
+          <t>18288</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>11318</t>
+          <t>11109</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28077</t>
+          <t>30409</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9991,32 +9991,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13707</t>
+          <t>13785</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8578</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>21131</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10026,32 +10026,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>32287</t>
+          <t>32073</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>23181</t>
+          <t>22672</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>45817</t>
+          <t>43809</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,33%</t>
         </is>
       </c>
     </row>
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>23693</t>
+          <t>27265</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>14886</t>
+          <t>18196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>34048</t>
+          <t>39837</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>23637</t>
+          <t>26539</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>16515</t>
+          <t>17924</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>33967</t>
+          <t>36632</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>47330</t>
+          <t>53805</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36522</t>
+          <t>42993</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62578</t>
+          <t>71308</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,55%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,68%</t>
         </is>
       </c>
     </row>
@@ -10182,17 +10182,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>414290</t>
+          <t>440858</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>414290</t>
+          <t>440858</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>414290</t>
+          <t>440858</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10217,17 +10217,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>345230</t>
+          <t>380958</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>345230</t>
+          <t>380958</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>345230</t>
+          <t>380958</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10252,17 +10252,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>759519</t>
+          <t>821815</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>759519</t>
+          <t>821815</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>759519</t>
+          <t>821815</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10299,32 +10299,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>320119</t>
+          <t>358124</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111550</t>
+          <t>337806</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>529314</t>
+          <t>373594</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>83,5%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10334,17 +10334,17 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>117673</t>
+          <t>132888</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>107863</t>
+          <t>121960</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124694</t>
+          <t>141547</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10369,32 +10369,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>437793</t>
+          <t>491012</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189489</t>
+          <t>467756</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>649166</t>
+          <t>508679</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>83,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>79,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>86,12%</t>
         </is>
       </c>
     </row>
@@ -10412,32 +10412,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28429</t>
+          <t>30312</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>19346</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>51737</t>
+          <t>45169</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
+          <t>7,07%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>4,51%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -10447,32 +10447,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14910</t>
+          <t>17305</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>10373</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>23849</t>
+          <t>28880</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -10482,32 +10482,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>43339</t>
+          <t>47618</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>13532</t>
+          <t>33826</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>72428</t>
+          <t>64581</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -10525,32 +10525,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>16743</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>9612</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34417</t>
+          <t>29901</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10560,32 +10560,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5177</t>
+          <t>5560</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2355</t>
+          <t>2435</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9729</t>
+          <t>10799</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10595,32 +10595,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>22303</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>7754</t>
+          <t>14029</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>39198</t>
+          <t>34453</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -10638,32 +10638,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>264268</t>
+          <t>23702</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>28304</t>
+          <t>13734</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>502517</t>
+          <t>35658</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>41,93%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10673,32 +10673,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5542</t>
+          <t>6063</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2512</t>
+          <t>2895</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>10739</t>
+          <t>12571</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10708,32 +10708,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>269810</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>31165</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>552356</t>
+          <t>43950</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -10751,17 +10751,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>630213</t>
+          <t>428881</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>630213</t>
+          <t>428881</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>630213</t>
+          <t>428881</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -10786,17 +10786,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>143301</t>
+          <t>161816</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>143301</t>
+          <t>161816</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>143301</t>
+          <t>161816</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -10821,17 +10821,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>773515</t>
+          <t>590697</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>773515</t>
+          <t>590697</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>773515</t>
+          <t>590697</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10868,32 +10868,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>803339</t>
+          <t>876661</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>777342</t>
+          <t>848748</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>822761</t>
+          <t>899613</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>86,65%</t>
+          <t>86,7%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>83,85%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,75%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10903,32 +10903,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>784190</t>
+          <t>643040</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>745207</t>
+          <t>625331</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>841533</t>
+          <t>660962</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>82,5%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10938,32 +10938,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1587529</t>
+          <t>1519700</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1546420</t>
+          <t>1488487</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1657002</t>
+          <t>1546676</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>85,9%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>87,43%</t>
         </is>
       </c>
     </row>
@@ -10981,32 +10981,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>47779</t>
+          <t>53691</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35027</t>
+          <t>38833</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>65397</t>
+          <t>70935</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11016,32 +11016,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>55843</t>
+          <t>61468</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>23917</t>
+          <t>48421</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>78007</t>
+          <t>75413</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11051,32 +11051,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>103621</t>
+          <t>115160</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>68708</t>
+          <t>96252</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>126715</t>
+          <t>140028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>6,51%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -11094,32 +11094,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>38270</t>
+          <t>40643</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>27859</t>
+          <t>27578</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>54540</t>
+          <t>57191</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11129,32 +11129,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>29913</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11431</t>
+          <t>22484</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>39236</t>
+          <t>40313</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11164,32 +11164,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>64480</t>
+          <t>70556</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43153</t>
+          <t>55990</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>84120</t>
+          <t>90373</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,11%</t>
         </is>
       </c>
     </row>
@@ -11207,32 +11207,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>37693</t>
+          <t>40128</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26703</t>
+          <t>28866</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>54207</t>
+          <t>56794</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11242,32 +11242,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>20814</t>
+          <t>23600</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8945</t>
+          <t>16283</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32470</t>
+          <t>33901</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11277,32 +11277,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>58507</t>
+          <t>63728</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>38536</t>
+          <t>50383</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>76601</t>
+          <t>83201</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -11320,17 +11320,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>927080</t>
+          <t>1011123</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>927080</t>
+          <t>1011123</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>927080</t>
+          <t>1011123</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11355,17 +11355,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>887058</t>
+          <t>758021</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>887058</t>
+          <t>758021</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>887058</t>
+          <t>758021</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11390,17 +11390,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1814138</t>
+          <t>1769144</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1814138</t>
+          <t>1769144</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1814138</t>
+          <t>1769144</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11437,32 +11437,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>340059</t>
+          <t>409413</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>319602</t>
+          <t>385408</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>355339</t>
+          <t>430893</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>82,48%</t>
+          <t>81,59%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>77,52%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>85,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11472,32 +11472,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>644752</t>
+          <t>611248</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>626296</t>
+          <t>594428</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>666998</t>
+          <t>626161</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>87,15%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11507,32 +11507,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>984811</t>
+          <t>1020661</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>955647</t>
+          <t>989940</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1017719</t>
+          <t>1044424</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>82,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>86,94%</t>
         </is>
       </c>
     </row>
@@ -11550,32 +11550,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>28018</t>
+          <t>37861</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18830</t>
+          <t>27091</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42628</t>
+          <t>57027</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -11585,32 +11585,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>35649</t>
+          <t>42116</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>23732</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>48423</t>
+          <t>53910</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -11620,32 +11620,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>63667</t>
+          <t>79978</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48383</t>
+          <t>62496</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>81214</t>
+          <t>99385</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -11663,67 +11663,67 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>23598</t>
+          <t>26556</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>14473</t>
+          <t>16193</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>37200</t>
+          <t>41754</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>3,23%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8,32%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>24521</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>16805</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>35337</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>3,51%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>18884</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>11667</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>26971</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>2,63%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -11733,32 +11733,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>42483</t>
+          <t>51077</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>29344</t>
+          <t>37053</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>60187</t>
+          <t>68000</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,66%</t>
         </is>
       </c>
     </row>
@@ -11776,32 +11776,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>20601</t>
+          <t>27978</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>15520</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>39973</t>
+          <t>49154</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -11811,32 +11811,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>19352</t>
+          <t>21598</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>11983</t>
+          <t>15022</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>30478</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -11846,32 +11846,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>39953</t>
+          <t>49576</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>26390</t>
+          <t>35614</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>59547</t>
+          <t>69177</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -11889,17 +11889,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>412275</t>
+          <t>501808</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>412275</t>
+          <t>501808</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>412275</t>
+          <t>501808</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -11924,17 +11924,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>718638</t>
+          <t>699483</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>718638</t>
+          <t>699483</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>718638</t>
+          <t>699483</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -11959,17 +11959,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1130913</t>
+          <t>1201291</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1130913</t>
+          <t>1201291</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1130913</t>
+          <t>1201291</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -11991,7 +11991,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -12006,7 +12006,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>182119</t>
+          <t>181591</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
@@ -12041,7 +12041,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>579488</t>
+          <t>638515</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
@@ -12076,7 +12076,7 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>761606</t>
+          <t>820106</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
@@ -12458,17 +12458,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>182119</t>
+          <t>181591</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>182119</t>
+          <t>181591</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>182119</t>
+          <t>181591</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -12493,17 +12493,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>579488</t>
+          <t>638515</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>579488</t>
+          <t>638515</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>579488</t>
+          <t>638515</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -12528,17 +12528,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>761606</t>
+          <t>820106</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>761606</t>
+          <t>820106</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>761606</t>
+          <t>820106</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -12575,32 +12575,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>2372327</t>
+          <t>2605330</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1766967</t>
+          <t>2557174</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>2596374</t>
+          <t>2649355</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>83,13%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>85,54%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -12610,32 +12610,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2744754</t>
+          <t>2706404</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2701954</t>
+          <t>2671477</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2816351</t>
+          <t>2737816</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,56%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>87,46%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>88,58%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -12645,32 +12645,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>5117080</t>
+          <t>5311734</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>4363683</t>
+          <t>5253735</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>5363764</t>
+          <t>5365093</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>86,13%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>71,25%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>87,58%</t>
+          <t>87,0%</t>
         </is>
       </c>
     </row>
@@ -12688,102 +12688,102 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>165520</t>
+          <t>188294</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>124220</t>
+          <t>155993</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>200226</t>
+          <t>220129</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>178084</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>155472</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>200869</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>5,76%</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>5,03%</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>6,5%</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>381</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>366378</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>333832</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>407084</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>5,41%</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
           <t>6,6%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>227</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>159664</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
-        <is>
-          <t>124985</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr">
-        <is>
-          <t>187129</t>
-        </is>
-      </c>
-      <c r="N35" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
-      <c r="O35" s="2" t="inlineStr">
-        <is>
-          <t>4,05%</t>
-        </is>
-      </c>
-      <c r="P35" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="Q35" s="2" t="inlineStr">
-        <is>
-          <t>381</t>
-        </is>
-      </c>
-      <c r="R35" s="2" t="inlineStr">
-        <is>
-          <t>325184</t>
-        </is>
-      </c>
-      <c r="S35" s="2" t="inlineStr">
-        <is>
-          <t>276438</t>
-        </is>
-      </c>
-      <c r="T35" s="2" t="inlineStr">
-        <is>
-          <t>368534</t>
-        </is>
-      </c>
-      <c r="U35" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="V35" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="W35" s="2" t="inlineStr">
-        <is>
-          <t>6,02%</t>
         </is>
       </c>
     </row>
@@ -12801,32 +12801,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>118741</t>
+          <t>129159</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>84868</t>
+          <t>106210</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>147508</t>
+          <t>157840</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -12836,32 +12836,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>81690</t>
+          <t>92108</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>61558</t>
+          <t>74937</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>99312</t>
+          <t>108915</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -12871,32 +12871,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>200431</t>
+          <t>221268</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>166998</t>
+          <t>193034</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>236305</t>
+          <t>254291</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -12914,32 +12914,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>378768</t>
+          <t>153366</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>136135</t>
+          <t>125742</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1052965</t>
+          <t>182666</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -12949,32 +12949,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>103115</t>
+          <t>114313</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>81108</t>
+          <t>97344</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>125689</t>
+          <t>136090</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -12984,32 +12984,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>481883</t>
+          <t>267679</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>231711</t>
+          <t>237653</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1306720</t>
+          <t>305548</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>4,95%</t>
         </is>
       </c>
     </row>
@@ -13027,17 +13027,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3035356</t>
+          <t>3076149</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3035356</t>
+          <t>3076149</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3035356</t>
+          <t>3076149</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -13062,17 +13062,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3089222</t>
+          <t>3090909</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3089222</t>
+          <t>3090909</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3089222</t>
+          <t>3090909</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -13097,17 +13097,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6124578</t>
+          <t>6167058</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6124578</t>
+          <t>6167058</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6124578</t>
+          <t>6167058</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
